--- a/pdf/01_撮影機材_低価格版とアップグレード版.xlsx
+++ b/pdf/01_撮影機材_低価格版とアップグレード版.xlsx
@@ -151,7 +151,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -178,8 +178,14 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -559,7 +565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K49"/>
+  <dimension ref="A1:L51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -573,6 +579,7 @@
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="54" customWidth="1" min="10" max="10"/>
     <col width="40" customWidth="1" min="11" max="11"/>
+    <col width="34" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -659,6 +666,11 @@
           <t>価格の確度</t>
         </is>
       </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>サクラチェッカー</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
@@ -707,6 +719,11 @@
           <t>低＝0円／上＝前回調査で実売を確認</t>
         </is>
       </c>
+      <c r="L7" s="12" t="inlineStr">
+        <is>
+          <t>https://sakura-checker.jp/search/B0CFZX734J/</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
@@ -759,6 +776,11 @@
           <t>低＝掲載に幅あり（3,012／6,018）／上＝店により幅あり（30,800〜40,800・表は銀一）</t>
         </is>
       </c>
+      <c r="L8" s="12" t="inlineStr">
+        <is>
+          <t>https://sakura-checker.jp/search/B0053CEPQU/</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
@@ -811,6 +833,11 @@
           <t>低＝前回調査で実売を確認／上＝中古の幅あり（50,100〜53,700・表は中央値）</t>
         </is>
       </c>
+      <c r="L9" s="12" t="inlineStr">
+        <is>
+          <t>https://sakura-checker.jp/search/B0055MFTHM/</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
@@ -863,6 +890,11 @@
           <t>低＝前回調査で実売を確認／上＝概算（セット構成で変わる）</t>
         </is>
       </c>
+      <c r="L10" s="12" t="inlineStr">
+        <is>
+          <t>https://sakura-checker.jp/search/B077Z61TPN/</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
@@ -911,9 +943,14 @@
           <t>低＝0円／上＝前回調査で実売を確認</t>
         </is>
       </c>
+      <c r="L11" s="12" t="inlineStr">
+        <is>
+          <t>https://sakura-checker.jp/search/B09J4GXV63/</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -963,9 +1000,14 @@
           <t>前回調査で実売を確認</t>
         </is>
       </c>
+      <c r="L12" s="12" t="inlineStr">
+        <is>
+          <t>https://sakura-checker.jp/search/B0CSL4PXDV/</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1015,9 +1057,14 @@
           <t>前回調査で実売を確認</t>
         </is>
       </c>
+      <c r="L13" s="12" t="inlineStr">
+        <is>
+          <t>https://sakura-checker.jp/search/B09MRLGL7G/</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1067,9 +1114,14 @@
           <t>前々回調査時の値（前回は再確認できず）</t>
         </is>
       </c>
+      <c r="L14" s="12" t="inlineStr">
+        <is>
+          <t>https://sakura-checker.jp/search/B0CHNY19K3/</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1119,9 +1171,14 @@
           <t>前回調査で実売を確認（1枚561円×2）</t>
         </is>
       </c>
+      <c r="L15" s="14" t="inlineStr">
+        <is>
+          <t>Amazon以外のため対象外</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1171,9 +1228,14 @@
           <t>概算（購入時に要確認）</t>
         </is>
       </c>
+      <c r="L16" s="12" t="inlineStr">
+        <is>
+          <t>https://sakura-checker.jp/search/B0C49DT18X/</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1223,9 +1285,14 @@
           <t>概算（商品ページ未特定・リンクは検索結果）</t>
         </is>
       </c>
+      <c r="L17" s="14" t="inlineStr">
+        <is>
+          <t>Amazon以外のため対象外</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1267,96 +1334,102 @@
           <t>低＝0円／上＝前回調査時の値（商品ページ未特定）</t>
         </is>
       </c>
+      <c r="L18" s="14" t="inlineStr">
+        <is>
+          <t>Amazon以外のため対象外</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="13" t="n"/>
-      <c r="B19" s="14" t="inlineStr">
+      <c r="A19" s="15" t="n"/>
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="C19" s="13" t="n"/>
-      <c r="D19" s="15">
+      <c r="C19" s="15" t="n"/>
+      <c r="D19" s="17">
         <f>SUM(D7:D18)</f>
         <v/>
       </c>
-      <c r="E19" s="13" t="n"/>
-      <c r="F19" s="13" t="n"/>
-      <c r="G19" s="15">
+      <c r="E19" s="15" t="n"/>
+      <c r="F19" s="15" t="n"/>
+      <c r="G19" s="17">
         <f>SUM(G7:G18)</f>
         <v/>
       </c>
-      <c r="H19" s="13" t="n"/>
-      <c r="I19" s="15">
+      <c r="H19" s="15" t="n"/>
+      <c r="I19" s="17">
         <f>G19-D19</f>
         <v/>
       </c>
-      <c r="J19" s="13" t="n"/>
-      <c r="K19" s="13" t="n"/>
+      <c r="J19" s="15" t="n"/>
+      <c r="K19" s="15" t="n"/>
+      <c r="L19" s="15" t="n"/>
     </row>
     <row r="21">
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="18" t="inlineStr">
         <is>
           <t>三つの選び方</t>
         </is>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="B22" s="17" t="inlineStr">
+      <c r="B22" s="19" t="inlineStr">
         <is>
           <t>① 低価格版のまま</t>
         </is>
       </c>
-      <c r="C22" s="13" t="n"/>
-      <c r="D22" s="18">
+      <c r="C22" s="15" t="n"/>
+      <c r="D22" s="20">
         <f>D19</f>
         <v/>
       </c>
-      <c r="E22" s="13" t="n"/>
-      <c r="F22" s="19" t="inlineStr">
+      <c r="E22" s="15" t="n"/>
+      <c r="F22" s="21" t="inlineStr">
         <is>
           <t>いま組んである最小構成。八本すべて撮り切れます。</t>
         </is>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="B23" s="17" t="inlineStr">
+      <c r="B23" s="19" t="inlineStr">
         <is>
           <t>② 音と支えだけ上げる（優先度A）</t>
         </is>
       </c>
-      <c r="C23" s="13" t="n"/>
-      <c r="D23" s="18">
+      <c r="C23" s="15" t="n"/>
+      <c r="D23" s="20">
         <f>D19+I7+I8</f>
         <v/>
       </c>
-      <c r="E23" s="13" t="n"/>
-      <c r="F23" s="19" t="inlineStr">
+      <c r="E23" s="15" t="n"/>
+      <c r="F23" s="21" t="inlineStr">
         <is>
           <t>マイクと三脚だけアップグレード。インタビュー四人分の声と、動かすカットの安定がいちばん変わります。</t>
         </is>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="B24" s="17" t="inlineStr">
+      <c r="B24" s="19" t="inlineStr">
         <is>
           <t>③ 全部上げる</t>
         </is>
       </c>
-      <c r="C24" s="13" t="n"/>
-      <c r="D24" s="18">
+      <c r="C24" s="15" t="n"/>
+      <c r="D24" s="20">
         <f>G19</f>
         <v/>
       </c>
-      <c r="E24" s="13" t="n"/>
-      <c r="F24" s="19" t="inlineStr">
+      <c r="E24" s="15" t="n"/>
+      <c r="F24" s="21" t="inlineStr">
         <is>
           <t>アップグレード版の合計。</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="20" t="inlineStr">
+      <c r="A27" s="22" t="inlineStr">
         <is>
           <t>価格について（必ずお読みください）</t>
         </is>
@@ -1401,7 +1474,7 @@
       <c r="A33" s="1" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="21" t="inlineStr">
+      <c r="A34" s="23" t="inlineStr">
         <is>
           <t>表の見かた</t>
         </is>
@@ -1439,7 +1512,7 @@
       <c r="A39" s="1" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="21" t="inlineStr">
+      <c r="A40" s="23" t="inlineStr">
         <is>
           <t>評価とサクラチェックについて</t>
         </is>
@@ -1469,36 +1542,50 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>・この環境からはサクラチェッカーを開けないため、自動判定はできていません。発注前にURLを貼って判定してください。</t>
+          <t>・サクラチェッカー（sakura-checker.jp）はこの環境から接続が遮断されており、こちらで判定を実行できませんでした。</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="inlineStr"/>
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　代わりに「サクラチェッカー」列に、商品ごとの判定ページへのリンクを入れてあります。クリックすれば数秒で判定が出ます。</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="21" t="inlineStr">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　Amazon以外の販売ページ（サインモール・銀一・楽天・価格.com）はサクラチェッカーの対象外です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="23" t="inlineStr">
         <is>
           <t>注意</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="inlineStr">
-        <is>
-          <t>・マクロレンズはソニーEマウント専用です。お使いのカメラが別マウントの場合は、同じ焦点距離帯のものに読み替えてください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>・アップグレード版のマクロレンズは中古価格です。新品にする場合は金額が上がります。</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>・マクロレンズはソニーEマウント専用です。お使いのカメラが別マウントの場合は、同じ焦点距離帯のものに読み替えてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>・アップグレード版のマクロレンズは中古価格です。新品にする場合は金額が上がります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
         <is>
           <t>・撮影するカットの一覧は別ファイル「02_場面別ショットリスト.xlsx」にあります。</t>
         </is>
@@ -1507,25 +1594,34 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pdf/01_撮影機材_低価格版とアップグレード版.xlsx
+++ b/pdf/01_撮影機材_低価格版とアップグレード版.xlsx
@@ -565,7 +565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:L59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -751,15 +751,15 @@
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>Manfrotto Befree live アルミニウムT三脚 ビデオ雲台キット（MVKBFRT-LIVE）</t>
+          <t>Velbon シェルパ 635III N（SHR635-3N）</t>
         </is>
       </c>
       <c r="G8" s="9" t="n">
-        <v>30800</v>
+        <v>25000</v>
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>https://www.ginichi.com/shop/products/detail.php?product_id=118199</t>
+          <t>https://www.amazon.co.jp/dp/B08N4QDVDF</t>
         </is>
       </c>
       <c r="I8" s="11">
@@ -768,12 +768,12 @@
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>フルード雲台になり、パン・ティルトがなめらかに止まる。三千円台の三脚は「置いて固定」はできるが、動かしながら撮るとカクつく</t>
+          <t>脚が太くなり（脚径29mm）四段から三段になるので、揺れが止まるまでが速い。EX-440は細い四段なので、伸ばすと録画の頭に微振動が乗る。全高も179cmまで伸び、クイックシューでカメラの付け外しが速い（一人で撮るときに効く）。ただし雲台は三ウェイなので、動かしながら撮るなめらかさはビデオ雲台に及ばない</t>
         </is>
       </c>
       <c r="K8" s="8" t="inlineStr">
         <is>
-          <t>低＝掲載に幅あり（3,012／6,018）／上＝店により幅あり（30,800〜40,800・表は銀一）</t>
+          <t>低＝掲載に幅あり（3,012／6,018）／上＝掲載に大きな開きあり（18,984〜39,800）・表はご指定の25,000で概算</t>
         </is>
       </c>
       <c r="L8" s="12" t="inlineStr">
@@ -1459,7 +1459,7 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>・幅があるもの：三脚（低3,012／6,018、上30,800〜40,800）、マクロレンズの上（中古50,100〜53,700）。</t>
+          <t>・幅があるもの：三脚（低3,012／6,018、上18,984〜39,800）、マクロレンズの上（中古50,100〜53,700）。</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1585,55 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="inlineStr">
+      <c r="A51" s="1" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="23" t="inlineStr">
+        <is>
+          <t>三脚のアップグレード候補（同じ二万五千円台で二つ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>・ベルボン シェルパ635III N ＝ 三ウェイ雲台／三段・脚径29mm／全高179cm（EV含む）・139cm（EV無し）／縮長67cm／質量2.43kg／耐荷重3kg（脚最大8kg）</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>・NEEWER LL27 ＝ フルード（ビデオ）雲台／全高89.4〜192cm／質量4.0kg／耐荷重8kg／アルミ合金／NEEWER公式24,999円</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>・据えて撮る画（③⑦の固定・①⑤⑥の真俯瞰）が中心で、一人で持ち運ぶ回数が多いならシェルパ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>・⑥の「工房を歩くカメラ」や①の横移動でパンを使うなら、フルード雲台のLL27。ただし4kgあり、持ち運びは重くなります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>・NEEWERは照明でも採用しているブランドですが、メーカー公式ではない量販ブランドです。発注前にサクラチェッカーでご確認ください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
         <is>
           <t>・撮影するカットの一覧は別ファイル「02_場面別ショットリスト.xlsx」にあります。</t>
         </is>
